--- a/config/random_tower/buffs.xlsx
+++ b/config/random_tower/buffs.xlsx
@@ -1547,7 +1547,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>味方の物攻+10%</t>
+          <t>我方物攻+10%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1614,7 +1614,7 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>味方の物攻+15%</t>
+          <t>我方物攻+15%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>味方の物攻+20%</t>
+          <t>我方物攻+20%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -1763,7 +1763,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>味方の特攻+10%</t>
+          <t>我方特攻+10%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -1830,7 +1830,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>味方の特攻+15%</t>
+          <t>我方特攻+15%</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1902,7 +1902,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>味方の特攻+20%</t>
+          <t>我方特攻+20%</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1979,7 +1979,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -2056,7 +2056,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+10%</t>
+          <t>我方的物攻和特攻+10%</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+15%</t>
+          <t>我方的物攻和特攻+15%</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -2220,7 +2220,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>味方のダメージバフ+5%</t>
+          <t>我方伤害增益 +5%</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2287,7 +2287,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>味方のダメージバフ+10%</t>
+          <t>我方伤害增益 +10%</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2359,7 +2359,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>味方のダメージバフ+15%</t>
+          <t>我方伤害增益 +15%</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2436,7 +2436,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>味方の会心率+5%</t>
+          <t>我方暴击率+5%</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2503,7 +2503,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>味方の会心率+10%</t>
+          <t>我方暴击率+10%</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>味方の会心率+15%</t>
+          <t>我方暴击率+15%</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -2652,7 +2652,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>味方の会心ダメージ+10%</t>
+          <t>我方暴击伤害+10%</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2719,7 +2719,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>味方の会心ダメージ+15%</t>
+          <t>我方暴击伤害+15%</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2791,7 +2791,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>味方の会心ダメージ+20%</t>
+          <t>我方暴击伤害+20%</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2868,7 +2868,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>味方の物防力+15%</t>
+          <t>我方物防力+15%</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2935,7 +2935,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>味方の物防力+20%</t>
+          <t>我方物防力+20%</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>味方の物防力+25%</t>
+          <t>我方物防力+25%</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -3084,7 +3084,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>味方の特防力+15%</t>
+          <t>我方特防力+15%</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -3151,7 +3151,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>味方の特防力+20%</t>
+          <t>我方特防力+20%</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -3223,7 +3223,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>味方の特防力+25%</t>
+          <t>我方特防力+25%</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -3300,7 +3300,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>味方の物防と特防力+10%</t>
+          <t>我方的物防和特防力+10%</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>味方の物防と特防力+15%</t>
+          <t>我方的物防和特防力+15%</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -3459,7 +3459,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>味方の物防と特防力+20%</t>
+          <t>我方的物防和特防力+20%</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>味方のダメージ耐性+5%</t>
+          <t>我方伤害减免+5%</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -3608,7 +3608,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>味方のダメージ耐性+10%</t>
+          <t>我方伤害减免+10%</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>味方のダメージ耐性+15%</t>
+          <t>我方伤害抗性+15%</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3757,7 +3757,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>味方の抵抗+10%</t>
+          <t>我方抵抗+10%</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3824,7 +3824,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>味方の抵抗+15%</t>
+          <t>我方抵抗+15%</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3891,7 +3891,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>味方の抵抗+20%</t>
+          <t>我方抵抗+20%</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>味方の吸血+4%</t>
+          <t>我方吸血+4%</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4025,7 +4025,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>味方の吸血+8%</t>
+          <t>我方吸血+8%</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -4092,7 +4092,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>味方の吸血+10%</t>
+          <t>我方吸血+10%</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -4159,7 +4159,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>味方1体のHPを25%回復</t>
+          <t>我方机体的生命值恢复25%</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>味方1体のHPを50%回復</t>
+          <t>我方机体生命值回复50%</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -4303,7 +4303,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>味方1体のHPを100%回復</t>
+          <t>我方机体的HP恢复100%</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -4375,7 +4375,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>味方1体のHPを25%回復</t>
+          <t>我方机体的生命值恢复25%</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -4447,7 +4447,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t>味方1体の覚醒値を200回復</t>
+          <t>1名伙伴的觉醒值回复200</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -4519,7 +4519,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>味方1体の覚醒値を500回復</t>
+          <t>1名伙伴的觉醒值回复500</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -4591,7 +4591,7 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t>味方1体の覚醒値を1000回復</t>
+          <t>1名伙伴的觉醒值回复1000</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4663,7 +4663,7 @@
       </c>
       <c r="C47" s="3" t="inlineStr">
         <is>
-          <t>味方1体の覚醒値を1000回復</t>
+          <t>1名伙伴的觉醒值回复1000</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4735,7 +4735,7 @@
       </c>
       <c r="C48" s="3" t="inlineStr">
         <is>
-          <t>味方1体を復活</t>
+          <t>复活一个伙伴</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4802,7 +4802,7 @@
       </c>
       <c r="C49" s="3" t="inlineStr">
         <is>
-          <t>味方1体を復活</t>
+          <t>复活一个伙伴</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="C50" s="3" t="inlineStr">
         <is>
-          <t>味方1体を復活</t>
+          <t>复活一个伙伴</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4936,7 +4936,7 @@
       </c>
       <c r="C51" s="3" t="inlineStr">
         <is>
-          <t>味方1体を復活</t>
+          <t>复活一个伙伴</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -5003,7 +5003,7 @@
       </c>
       <c r="C52" s="3" t="inlineStr">
         <is>
-          <t>編成した味方のHPを全回復</t>
+          <t>将我方的HP全部回复</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="C53" s="3" t="inlineStr">
         <is>
-          <t>編成した味方の覚醒値を全回復</t>
+          <t>将编成的伙伴的觉醒值全部恢复</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -5147,7 +5147,7 @@
       </c>
       <c r="C54" s="3" t="inlineStr">
         <is>
-          <t>味方1体を復活</t>
+          <t>复活一个伙伴</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -5214,7 +5214,7 @@
       </c>
       <c r="C55" s="3" t="inlineStr">
         <is>
-          <t>戦闘終了時に残りターン数*2のポイントを追加獲得できる</t>
+          <t>战斗结束时可额外获得剩余回合数*2的点数</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="C56" s="3" t="inlineStr">
         <is>
-          <t>戦闘終了時に生存した味方の数*1のポイントを追加獲得できる</t>
+          <t>战斗结束时可额外获得生存的伙伴数*1的点数</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -5353,7 +5353,7 @@
       </c>
       <c r="C57" s="3" t="inlineStr">
         <is>
-          <t>戦闘終了時に生存した味方の数*2のポイントを追加獲得できる</t>
+          <t>战斗结束时可额外获得生存伙伴数量*2的点数</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
@@ -5420,7 +5420,7 @@
       </c>
       <c r="C58" s="3" t="inlineStr">
         <is>
-          <t>戦闘終了時に現在の階層数*2のポイントを追加獲得できる</t>
+          <t>战斗结束时可额外获得当前层数*2点</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5565,7 +5565,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>味方の物攻+20%</t>
+          <t>我方物攻+20%</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5637,7 +5637,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>味方の特攻+20%</t>
+          <t>我方特攻+20%</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5709,7 +5709,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+15%</t>
+          <t>我方的物攻和特攻+15%</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5786,7 +5786,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>味方のダメージバフ+20%</t>
+          <t>我方伤害增益 +20%</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5858,7 +5858,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>味方の会心率+20%</t>
+          <t>我方暴击率+20%</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5930,7 +5930,7 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>味方の会心ダメージ+30%</t>
+          <t>我方暴击伤害+30%</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -6003,7 +6003,7 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>味方の物防力+30%</t>
+          <t>我方物防力+30%</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -6075,7 +6075,7 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>味方の特防力+30%</t>
+          <t>我方特防力+30%</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -6147,7 +6147,7 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>味方の物防と特防力+25%</t>
+          <t>我方的物防和特防力+25%</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>味方のダメージ耐性+20%</t>
+          <t>我方伤害减免+20%</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6299,7 +6299,7 @@
       </c>
       <c r="C75" s="3" t="inlineStr">
         <is>
-          <t>現在のHP値が10%減少</t>
+          <t>当前HP值减少10%</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
@@ -6351,7 +6351,7 @@
       </c>
       <c r="C76" s="3" t="inlineStr">
         <is>
-          <t>現在のHP値が20%減少</t>
+          <t>当前HP值减少20%</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6403,7 +6403,7 @@
       </c>
       <c r="C77" s="3" t="inlineStr">
         <is>
-          <t>現在のHP値が30%減少</t>
+          <t>当前HP值减少30%</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6455,7 +6455,7 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>現在の覚醒値が200減少</t>
+          <t>当前觉醒值减少200</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6507,7 +6507,7 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>現在の覚醒値が500減少</t>
+          <t>当前觉醒值减少500</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6559,7 +6559,7 @@
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>現在の覚醒値が1000減少</t>
+          <t>当前觉醒值减少1000</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>現在の覚醒値が500上昇</t>
+          <t>当前觉醒值提升500</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6663,7 +6663,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>味方の速度-20%</t>
+          <t>我方速度-20%</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6720,7 +6720,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>味方の速度-40%</t>
+          <t>我方速度-40%</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -6777,7 +6777,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>編成した味方のHPを全回復</t>
+          <t>将我方的HP全部回复</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -6829,7 +6829,7 @@
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>編成した味方の覚醒値を全回復</t>
+          <t>将编成的伙伴的觉醒值全部恢复</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -6881,7 +6881,7 @@
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>味方の物攻-5%</t>
+          <t>我方物攻-5%</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
@@ -6938,7 +6938,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>味方の特攻-5%</t>
+          <t>我方特攻-5%</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
@@ -6995,7 +6995,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>編成した味方のHPが20%回復</t>
+          <t>被编成的伙伴的HP回复20%</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7047,7 +7047,7 @@
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>編成した味方の覚醒値が200増加</t>
+          <t>被编成的伙伴的觉醒值增加200</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7100,7 +7100,7 @@
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>味方のHPが40%以下の時、攻撃のたびにダメージが10%上昇する(重複可能)。</t>
+          <t>我方生命值40%以下时，每次攻击伤害上升10%（可重复）。</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7172,7 +7172,7 @@
       </c>
       <c r="C92" s="3" t="inlineStr">
         <is>
-          <t>味方がHPを10%失うごとに、ダメージが8%上昇する。</t>
+          <t>盟友每损失10%生命值，伤害提升8%。</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7239,7 +7239,7 @@
       </c>
       <c r="C93" s="3" t="inlineStr">
         <is>
-          <t>敵にダメージを与えるたびに、自身の失ったHP8%の確定ダメージを追加付与する。</t>
+          <t>每次对敌人造成伤害时，追加自身损失HP8%的真实伤害。</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7306,7 +7306,7 @@
       </c>
       <c r="C94" s="3" t="inlineStr">
         <is>
-          <t>敵にダメージを与えるたびに、敵の失ったHP5%の確定ダメージを追加付与する。</t>
+          <t>每次对敌人造成伤害时，追加敌人损失5% HP的真实伤害。</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7373,7 +7373,7 @@
       </c>
       <c r="C95" s="3" t="inlineStr">
         <is>
-          <t>自身の攻撃力が現在の防御力の30%上昇する。</t>
+          <t>自身攻击力比当前防御力上升30%。</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7445,7 +7445,7 @@
       </c>
       <c r="C96" s="3" t="inlineStr">
         <is>
-          <t>戦闘で初回スキルを発動時、会心率バフを追加で50%獲得する。</t>
+          <t>战斗中发动初回技能时，暴击率增益额外获得50%。</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="C97" s="3" t="inlineStr">
         <is>
-          <t>スキルを発動するたびに、ダメージバフが追加で10%上昇する(戦闘終了まで持続)。</t>
+          <t>每发动一项技能，伤害加成提升10%（持续至战斗结束）。</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
@@ -7579,7 +7579,7 @@
       </c>
       <c r="C98" s="3" t="inlineStr">
         <is>
-          <t>通常攻撃またはスキルを発動するたびに、次のスキル発動時のダメージが10%上昇する(スキル発動後に消失)。</t>
+          <t>每次发动普通攻击或技能时，下一次技能发动时的伤害上升10%（技能发动后消失）。</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -7646,7 +7646,7 @@
       </c>
       <c r="C99" s="3" t="inlineStr">
         <is>
-          <t>味方のHPが50以下の時、ダメージ耐性を20%獲得する(戦闘終了まで持続)。</t>
+          <t>我方的生命值在50以下时，获得20%的伤害减免（持续到战斗结束）。</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -7713,7 +7713,7 @@
       </c>
       <c r="C100" s="3" t="inlineStr">
         <is>
-          <t>味方のHPが30以下の時、追加で吸血が30%上昇する(戦闘終了まで持続)。</t>
+          <t>我方生命值在30以下时，吸血值增加30%（持续至战斗结束）。</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -7780,7 +7780,7 @@
       </c>
       <c r="C101" s="3" t="inlineStr">
         <is>
-          <t>ダメージを受けるたびに、物防と特防が15%上昇する(最大3回重複可能、2ターン持続)。</t>
+          <t>受到伤害时，物防和特防上升15%（最多可重复3次，持续2回合）。</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -7847,7 +7847,7 @@
       </c>
       <c r="C102" s="3" t="inlineStr">
         <is>
-          <t>味方の現在のHPが10%減少するたびに、吸血が5%上昇する。</t>
+          <t>我方当前生命值每减少10%，吸血值上升5%。</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -7914,7 +7914,7 @@
       </c>
       <c r="C103" s="3" t="inlineStr">
         <is>
-          <t>自身の全ての吸血バフをシールドに転換(シールド=HP上限*吸血率*1.5、2ターン持続)。</t>
+          <t>自身所有吸血增益转换为护盾（护盾=生命上限*吸血率*1.5，持续2回合）。</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -7986,7 +7986,7 @@
       </c>
       <c r="C104" s="3" t="inlineStr">
         <is>
-          <t>シールド発動時、制御効果を無効化する。</t>
+          <t>护盾发动时，控制效果无效化。</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8053,7 +8053,7 @@
       </c>
       <c r="C105" s="3" t="inlineStr">
         <is>
-          <t>味方がダメージを受けた時、5%の確率で攻撃者を沈黙させる(1ターン持続)。</t>
+          <t>我方受到伤害时，有5%的概率使攻击者沉默（持续1回合）。</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8120,7 +8120,7 @@
       </c>
       <c r="C106" s="3" t="inlineStr">
         <is>
-          <t>戦闘開始時、覚醒値を追加で100獲得する。</t>
+          <t>战斗开始时，觉醒值额外获得100。</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -8182,7 +8182,7 @@
       </c>
       <c r="C107" s="3" t="inlineStr">
         <is>
-          <t>敵を撃破した時、覚醒値を追加で100獲得する。</t>
+          <t>击败敌人时，额外获得100点觉醒值。</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -8244,7 +8244,7 @@
       </c>
       <c r="C108" s="3" t="inlineStr">
         <is>
-          <t>ダメージを受けた時、覚醒値を追加で100獲得する。</t>
+          <t>受到伤害时，额外获得100点觉醒值。</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -8306,7 +8306,7 @@
       </c>
       <c r="C109" s="3" t="inlineStr">
         <is>
-          <t>フィード上の仲間に現在の属性*5%（第1属性を計算）の物攻と特攻を付与する。</t>
+          <t>给予饲料上的伙伴当前属性*5%（计算第1属性）的物攻和特攻。</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -8378,7 +8378,7 @@
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>ランダムな味方1体が戦闘するたびに、20%の物攻と特攻の属性バフを獲得する。</t>
+          <t>1个随机伙伴战斗时，获得20%的物攻和特攻属性增益。</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -8445,7 +8445,7 @@
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>編成中の仲間属性（第1属性を計算）を計算し、一番多い属性に仲間の物攻と特攻を*5%追加上昇する。</t>
+          <t>计算编成中的伙伴属性（计算第1属性），最多的属性使伙伴的物攻和特攻增加*5%。</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -8517,7 +8517,7 @@
       </c>
       <c r="C112" s="3" t="inlineStr">
         <is>
-          <t>特攻ダメージを与えた時、会心率が5%上昇する（2ターン持続、最大4段重複、重複持続時間を更新)。</t>
+          <t>给予特攻伤害时，暴击率上升5%（持续2回合，最多4段重复，重复持续时间更新）。</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -8579,7 +8579,7 @@
       </c>
       <c r="C113" s="3" t="inlineStr">
         <is>
-          <t>特攻バフを20%獲得するたびに、追加で物攻バフを10%獲得できる。</t>
+          <t>每次获得20%的特攻增益，可额外获得10%的物攻增益。</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="C114" s="3" t="inlineStr">
         <is>
-          <t>会心ダメージが20%上昇し、会心ダメージを付与した時に自身のHP上限10%のHPを回復する。</t>
+          <t>暴击伤害上升20%，给予暴击伤害时回复自身生命值上限10%的生命值。</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="C115" s="3" t="inlineStr">
         <is>
-          <t>物攻バフを20%獲得するたびに、追加で特攻バフを10%獲得できる。</t>
+          <t>每次获得20%的物攻增益，可额外获得10%的特攻增益。</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -8770,7 +8770,7 @@
       </c>
       <c r="C116" s="3" t="inlineStr">
         <is>
-          <t>制御された敵にダメージを与える時、その制御効果を解除し、現在のHP50%*のダメージを与える。</t>
+          <t>对被控制的敌人造成伤害时，解除控制效果，造成当前生命值50%*的伤害。</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -8842,7 +8842,7 @@
       </c>
       <c r="C117" s="3" t="inlineStr">
         <is>
-          <t>特攻で会心ダメージを与えた際、追加で会心ダメージが20%上昇し、上昇分の5%相当のHPを回復する。</t>
+          <t>特攻造成暴击伤害时，暴击伤害增加20%，回复上升部分的5% HP。</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -8904,7 +8904,7 @@
       </c>
       <c r="C118" s="3" t="inlineStr">
         <is>
-          <t>ビッグターンが終了するたびに、味方全員のランダムな制御効果を1つ解除する。</t>
+          <t>大回合结束时，解除我方全体人员的一个随机控制效果。</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -8971,7 +8971,7 @@
       </c>
       <c r="C119" s="3" t="inlineStr">
         <is>
-          <t>攻撃時、目標のデバフダメージを計算し、残りのダメージを即時発動する。</t>
+          <t>攻击时，计算目标的减益伤害，立即发动剩余的伤害。</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -9038,7 +9038,7 @@
       </c>
       <c r="C120" s="3" t="inlineStr">
         <is>
-          <t>ターン開始時に自身のデバフ効果を1つ解除する。1つ解除するたびに、そのターンでダメージバフをとダメージ耐性を5%獲得する(最大4回重複可能)。</t>
+          <t>回合开始时解除一个自身减益效果。每解除一个，该回合获得5%的伤害增益和伤害抗性（最多可重复4次）。</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -9105,7 +9105,7 @@
       </c>
       <c r="C121" s="3" t="inlineStr">
         <is>
-          <t>攻撃を受けた時、目標の特攻と物攻を5%減少する(最大6重複可能)。</t>
+          <t>受到攻击时，目标的特攻和物攻减少5%（最多可重复6次）。</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -9172,7 +9172,7 @@
       </c>
       <c r="C122" s="3" t="inlineStr">
         <is>
-          <t>吸血バフを2%持つごとに、追加でダメージバフが1%上昇する。</t>
+          <t>每拥有2%吸血增益，伤害增益额外上升1%。</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="C123" s="3" t="inlineStr">
         <is>
-          <t>攻撃するたびに、敵の物攻と特攻を10減少する(永久持続、2ターン持続、4段重複可能)。</t>
+          <t>每次攻击，敌人的物攻和特攻减少10（永久持续，持续2回合，可重复4段）。</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -9306,7 +9306,7 @@
       </c>
       <c r="C124" s="3" t="inlineStr">
         <is>
-          <t>吸血バフを2持つごとに、追加でダメージバフが1%上昇する。</t>
+          <t>每拥有2个吸血增益，伤害增益额外上升1%。</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -9373,7 +9373,7 @@
       </c>
       <c r="C125" s="3" t="inlineStr">
         <is>
-          <t>ダメージを与えると、現在のダメージの回復量を獲得する。</t>
+          <t>造成伤害后，获得当前伤害的回复量。</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -9440,7 +9440,7 @@
       </c>
       <c r="C126" s="3" t="inlineStr">
         <is>
-          <t>ダメージを与えるたびに、シールド値のダメージを追加付与する。</t>
+          <t>造成伤害时，追加护盾值的伤害。</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -9507,7 +9507,7 @@
       </c>
       <c r="C127" s="3" t="inlineStr">
         <is>
-          <t>ダメージを与える時、追加で現在のシールドとHPのダメージが上昇する。</t>
+          <t>造成伤害时，当前护盾和生命值的伤害额外上升。</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -9574,7 +9574,7 @@
       </c>
       <c r="C128" s="3" t="inlineStr">
         <is>
-          <t>次の戦闘で、味方が敵を倒すと攻撃バフ100%を獲得できる(2ターン持続)。</t>
+          <t>在下一场战斗中，我方打倒敌人时获得100%攻击增益（持续2回合）。</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -9636,7 +9636,7 @@
       </c>
       <c r="C129" s="3" t="inlineStr">
         <is>
-          <t>次の戦闘開始時、最初に行動する味方の与ダメージが2倍になる。</t>
+          <t>下次战斗开始时，最先行动的伙伴造成的伤害加倍。</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -9698,7 +9698,7 @@
       </c>
       <c r="C130" s="3" t="inlineStr">
         <is>
-          <t>次の戦闘開始時、15%の確率で敵の現在のHPを半減する(初回戦闘時のみ、1回まで発動)。</t>
+          <t>下次战斗开始时，有15%的机率将敌人当前的生命值减半（仅初次战斗时，最多发动1次）。</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -9760,7 +9760,7 @@
       </c>
       <c r="C131" s="3" t="inlineStr">
         <is>
-          <t>次の戦闘開始時、敵は50%の確率で即敗北する(敵単独で確率を計算)。</t>
+          <t>下次战斗开始时，敌人有50%的机率立即败北（敌人单独计算机率）。</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -9822,7 +9822,7 @@
       </c>
       <c r="C132" s="3" t="inlineStr">
         <is>
-          <t>1つの属性の味方が発動するたびに、追加でダメージ耐性を2%獲得する。</t>
+          <t>每发动一个属性的伙伴，额外获得2%的伤害减免。</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -9889,7 +9889,7 @@
       </c>
       <c r="C133" s="3" t="inlineStr">
         <is>
-          <t>味方全員の制御耐性が30%上昇する。</t>
+          <t>全体伙伴的控制耐性提高30%。</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -9956,7 +9956,7 @@
       </c>
       <c r="C134" s="3" t="inlineStr">
         <is>
-          <t>防御力が5%上昇ごとに(時空激戦バフ、特殊戦闘バフ、バフ)反撃ダメージが5%上昇する。</t>
+          <t>防御力每上升5%（时空激战增益、特殊战斗增益、增益）反击伤害上升5%。</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -10018,7 +10018,7 @@
       </c>
       <c r="C135" s="3" t="inlineStr">
         <is>
-          <t>ダメージを与えるたびに、ダメージ5%のシールドを獲得できる。</t>
+          <t>造成伤害时，可获得5%伤害护盾。</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -10085,7 +10085,7 @@
       </c>
       <c r="C136" s="3" t="inlineStr">
         <is>
-          <t>回復時にHPを超過した回復分がシールド値2に変わる。</t>
+          <t>回复时超过HP的回复量变成护盾值2。</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -10152,7 +10152,7 @@
       </c>
       <c r="C137" s="3" t="inlineStr">
         <is>
-          <t>味方が最初に戦闘不能になった時、次のターン開始前に復活し、HP50%と覚醒値100%を回復する(1回のみ発動)。</t>
+          <t>我方最初无法战斗时，在下回合开始前复活，回复50%的生命值和100%的觉醒值（仅发动1次）。</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -10214,7 +10214,7 @@
       </c>
       <c r="C138" s="3" t="inlineStr">
         <is>
-          <t>ターン開始ごとに、ランダムな敵1体に眩暈を1付与する。</t>
+          <t>每回合开始，给予1个随机敌人1个眩晕。</t>
         </is>
       </c>
       <c r="D138" t="inlineStr">
@@ -10281,7 +10281,7 @@
       </c>
       <c r="C139" s="3" t="inlineStr">
         <is>
-          <t>味方の制御率が20%上昇する。</t>
+          <t>我方控制率上升20%。</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -10348,7 +10348,7 @@
       </c>
       <c r="C140" s="3" t="inlineStr">
         <is>
-          <t>中毒、流血、火傷のダメージが1上昇する。</t>
+          <t>中毒，流血和烧伤伤害提高1。</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -10415,7 +10415,7 @@
       </c>
       <c r="C141" s="3" t="inlineStr">
         <is>
-          <t>中毒、流血、火傷のダメージが10%増加。</t>
+          <t>中毒、流血和烧伤造成的伤害提高10%。</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="C142" s="3" t="inlineStr">
         <is>
-          <t>次の戦闘開始時、全ての敵が沈黙する(1ターン持続)。</t>
+          <t>下次战斗开始时，所有敌人沉默（持续1回合）。</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -10544,7 +10544,7 @@
       </c>
       <c r="C143" s="3" t="inlineStr">
         <is>
-          <t>次の戦闘開始時、全ての敵に睡眠状態を付与する(1ターン持続)。</t>
+          <t>下次战斗开始时，给予全部敌人睡眠状态（持续1回合）。</t>
         </is>
       </c>
       <c r="D143" t="inlineStr">
@@ -10606,7 +10606,7 @@
       </c>
       <c r="C144" s="3" t="inlineStr">
         <is>
-          <t>戦闘開始時、全味方が現在の属性（第1属性を計算）*50%のゲージ値を追加で獲得できる。</t>
+          <t>战斗开始时，所有伙伴可额外获得当前属性（计算第1属性）*50%的量规值。</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -10673,7 +10673,7 @@
       </c>
       <c r="C145" s="3" t="inlineStr">
         <is>
-          <t>1つ目の属性が同じ味方を4体以上いる編成している場合、戦闘開始時にその属性を持つ味方の初期覚醒値値が500になる。</t>
+          <t>第1个属性相同的伙伴4只以上编成的场合，战斗开始时拥有该属性的伙伴的初始觉醒值值为500。</t>
         </is>
       </c>
       <c r="D145" t="inlineStr">
@@ -10740,7 +10740,7 @@
       </c>
       <c r="C146" s="3" t="inlineStr">
         <is>
-          <t>HPが40%以下の時、怒気の回復効果が2倍になる。</t>
+          <t>生命值40%以下时，怒气回复效果变为2倍。</t>
         </is>
       </c>
       <c r="D146" t="inlineStr">
@@ -10807,7 +10807,7 @@
       </c>
       <c r="C147" s="3" t="inlineStr">
         <is>
-          <t>次の戦闘開始時、味方の初期覚醒値1000を獲得する。</t>
+          <t>下次战斗开始时，获得我方初始觉醒值1000。</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
@@ -10870,7 +10870,7 @@
       </c>
       <c r="C149" s="3" t="inlineStr">
         <is>
-          <t>戦闘開始後、味方が自身の失ったHPのシールド値を獲得する(2ターン持続)。</t>
+          <t>战斗开始后，我方获得自身失去的生命值的护盾值（持续2回合）。</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -10937,7 +10937,7 @@
       </c>
       <c r="C150" s="3" t="inlineStr">
         <is>
-          <t>味方がHPを10%失うごとに、ダメージ耐性を8%獲得する(1ターン目持続)。</t>
+          <t>我方每损失10%的生命值，获得8%的伤害减免（持续第一回合）。</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -11004,7 +11004,7 @@
       </c>
       <c r="C151" s="3" t="inlineStr">
         <is>
-          <t>2ターン目の戦闘時、敵全体の全ての覚醒値をリセットする。</t>
+          <t>第2回合战斗时，重置全体敌人的全部觉醒值。</t>
         </is>
       </c>
       <c r="D151" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="C152" s="3" t="inlineStr">
         <is>
-          <t>味方が戦闘不能である時、生存している残りの味方は最大HP20%と覚醒値が500回復する。</t>
+          <t>当我方无法战斗时，剩余生存的我方最大生命值回复20%，觉醒值回复500。</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -11128,7 +11128,7 @@
       </c>
       <c r="C153" s="3" t="inlineStr">
         <is>
-          <t>味方のターン終了時に自身の失ったHP15%を回復する。</t>
+          <t>我方回合结束时回复自身损失的15%生命值。</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -11185,7 +11185,7 @@
       </c>
       <c r="C154" s="3" t="inlineStr">
         <is>
-          <t>味方の必殺スキル発動時、10%の確率で覚醒が100%即回復する。</t>
+          <t>我方必杀技能发动时，有10%的机率觉醒100%立即回复。</t>
         </is>
       </c>
       <c r="D154" t="inlineStr">
@@ -11247,7 +11247,7 @@
       </c>
       <c r="C155" s="3" t="inlineStr">
         <is>
-          <t>ターン開始ごとに、ランダムな敵1体をマークして、その被ダメージが追加で50%上昇する。</t>
+          <t>每回合开始时，标记1个随机敌人，其受到的伤害增加50%。</t>
         </is>
       </c>
       <c r="D155" t="inlineStr">
@@ -11309,7 +11309,7 @@
       </c>
       <c r="C156" s="3" t="inlineStr">
         <is>
-          <t>味方のスキル発動時、速度が20%上昇、覚醒値が200増加する。</t>
+          <t>我方技能发动时，速度上升20%，觉醒值增加200。</t>
         </is>
       </c>
       <c r="D156" t="inlineStr">
@@ -11371,7 +11371,7 @@
       </c>
       <c r="C157" s="3" t="inlineStr">
         <is>
-          <t>味方の属性相関効果が上昇し、有利属性のパートナーに20%のダメージを追加で与える。</t>
+          <t>我方属性相关效果上升，对有利属性的伙伴造成20%额外伤害。</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
@@ -11433,7 +11433,7 @@
       </c>
       <c r="C158" s="3" t="inlineStr">
         <is>
-          <t>味方が敵を撃破した時、自身のHP10%と覚醒値200を回復する。</t>
+          <t>我方击破敌人时，回复自身10%的生命值和200的觉醒值。</t>
         </is>
       </c>
       <c r="D158" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="C159" s="3" t="inlineStr">
         <is>
-          <t>ターン終了するごとに、HPが10%以下の敵はそのまま退場する。</t>
+          <t>每回合结束，生命值在10%以下的敌人就那样退场。</t>
         </is>
       </c>
       <c r="D159" t="inlineStr">
@@ -11557,7 +11557,7 @@
       </c>
       <c r="C160" s="3" t="inlineStr">
         <is>
-          <t>戦闘の最初のターンに味方全体の速度が20%上昇する。</t>
+          <t>战斗的第一个回合，我方全体速度上升20%。</t>
         </is>
       </c>
       <c r="D160" t="inlineStr">
@@ -11619,7 +11619,7 @@
       </c>
       <c r="C161" s="3" t="inlineStr">
         <is>
-          <t>味方の*4%属性速度が上昇する（第1属性を計算）。</t>
+          <t>盟友的属性速度提升*4%（计算第一属性）。</t>
         </is>
       </c>
       <c r="D161" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="C162" s="3" t="inlineStr">
         <is>
-          <t>前列の味方が50%の確率で制御効果を無効化する。</t>
+          <t>前排的伙伴有50%的概率使控制效果无效化。</t>
         </is>
       </c>
       <c r="D162" t="inlineStr">
@@ -11753,7 +11753,7 @@
       </c>
       <c r="C163" s="3" t="inlineStr">
         <is>
-          <t>敵のHP上限の10%減少する(永久持続)。</t>
+          <t>减少敌人生命值上限10%（永久持续）。</t>
         </is>
       </c>
       <c r="D163" t="inlineStr">
@@ -11821,7 +11821,7 @@
       </c>
       <c r="C165" s="3" t="inlineStr">
         <is>
-          <t>味方が撃破された時、攻撃者に同等のダメージを与える。</t>
+          <t>己方被击破时，给予攻击者同等伤害。</t>
         </is>
       </c>
       <c r="D165" t="inlineStr">
@@ -11883,7 +11883,7 @@
       </c>
       <c r="C166" s="3" t="inlineStr">
         <is>
-          <t>敵を撃破した時、その周囲の敵に与ダメージ40%のダメージを与える。</t>
+          <t>击破敌人时，对周围敌人造成40%伤害。</t>
         </is>
       </c>
       <c r="D166" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="C167" s="3" t="inlineStr">
         <is>
-          <t>味方が攻撃時、20%の確率で敵の覚醒値を50奪取する。</t>
+          <t>我方攻击时，有20%的机率夺取敌人50点觉醒值。</t>
         </is>
       </c>
       <c r="D167" t="inlineStr">
@@ -12007,7 +12007,7 @@
       </c>
       <c r="C168" s="3" t="inlineStr">
         <is>
-          <t>味方の治癒率が30%上昇する。</t>
+          <t>我方治愈几率上升30%。</t>
         </is>
       </c>
       <c r="D168" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="C169" s="3" t="inlineStr">
         <is>
-          <t>味方の必殺スキル発動時、敵の全バフを解除する。</t>
+          <t>我方必杀技能发动时，解除敌方全部增益。</t>
         </is>
       </c>
       <c r="D169" t="inlineStr">
@@ -12131,7 +12131,7 @@
       </c>
       <c r="C170" s="3" t="inlineStr">
         <is>
-          <t>奇数ターンで味方の致命ダメージが30%上昇し、偶数ターンで15%減少する。</t>
+          <t>奇数回合己方的致命伤害上升30%，偶数回合减少15%。</t>
         </is>
       </c>
       <c r="D170" t="inlineStr">
@@ -12193,7 +12193,7 @@
       </c>
       <c r="C171" s="3" t="inlineStr">
         <is>
-          <t>ターン終了ごとに、敵全員に攻撃力が最も高い味方の攻撃力20%の確定ダメージを与える。</t>
+          <t>每回合结束时，对全体敌人造成攻击力最高的我方攻击力20%的真实伤害。</t>
         </is>
       </c>
       <c r="D171" t="inlineStr">
@@ -12255,7 +12255,7 @@
       </c>
       <c r="C172" s="3" t="inlineStr">
         <is>
-          <t>戦闘開始時、全体シールドを1つ獲得する。シールドは味方全員の被ダメージを吸収し、吸収値は味方内の最高HPと同等。</t>
+          <t>战斗开始时获得1个全体护盾。护盾吸收我方全员的受伤害，吸收值与我方最高HP同等。</t>
         </is>
       </c>
       <c r="D172" t="inlineStr">
@@ -12317,7 +12317,7 @@
       </c>
       <c r="C173" s="3" t="inlineStr">
         <is>
-          <t>味方の与える持続ダメージが倍増する。</t>
+          <t>我方造成的持续伤害加倍。</t>
         </is>
       </c>
       <c r="D173" t="inlineStr">
@@ -12384,7 +12384,7 @@
       </c>
       <c r="C174" s="3" t="inlineStr">
         <is>
-          <t>戦闘の最初のターンで覚醒値がMAXとなり、致命ダメージが20%ターン減少する。</t>
+          <t>战斗的最初回合觉醒值最大，致命伤害减少20%回合。</t>
         </is>
       </c>
       <c r="D174" t="inlineStr">
@@ -12447,7 +12447,7 @@
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+10%</t>
+          <t>我方的物攻和特攻+10%</t>
         </is>
       </c>
       <c r="D176" t="inlineStr">
@@ -12524,7 +12524,7 @@
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+10%</t>
+          <t>我方的物攻和特攻+10%</t>
         </is>
       </c>
       <c r="D177" t="inlineStr">
@@ -12601,7 +12601,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+10%</t>
+          <t>我方的物攻和特攻+10%</t>
         </is>
       </c>
       <c r="D178" t="inlineStr">
@@ -12678,7 +12678,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D179" t="inlineStr">
@@ -12755,7 +12755,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D180" t="inlineStr">
@@ -12832,7 +12832,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D181" t="inlineStr">
@@ -12909,7 +12909,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D182" t="inlineStr">
@@ -12986,7 +12986,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D183" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D184" t="inlineStr">
@@ -13140,7 +13140,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D185" t="inlineStr">
@@ -13217,7 +13217,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D186" t="inlineStr">
@@ -13294,7 +13294,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D187" t="inlineStr">
@@ -13371,7 +13371,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D188" t="inlineStr">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D189" t="inlineStr">
@@ -13525,7 +13525,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D190" t="inlineStr">
@@ -13603,7 +13603,7 @@
       </c>
       <c r="C192" s="3" t="inlineStr">
         <is>
-          <t>【火の力】敵にダメージを与えるたびに、自身の10%を超えない範囲でその特攻、物攻を8%減少し、【悪の力】は追加効果を上昇する。</t>
+          <t>【火之力】对敌人造成伤害时，在不超过自身10%的范围内减少其特攻、物攻8%，【恶之力】提升追加效果。</t>
         </is>
       </c>
       <c r="D192" t="inlineStr">
@@ -13660,7 +13660,7 @@
       </c>
       <c r="C193" s="3" t="inlineStr">
         <is>
-          <t>【水の力】敵にダメージを与えるたびに、自身の10%を超えない範囲でその8%物防、物防を8%減少し、【悪の力】は追加効果を上昇する。</t>
+          <t>【水之力】对敌人造成伤害时，在不超过自身10%的范围内减少8%物防，物防减少8%，【恶之力】提升追加效果。</t>
         </is>
       </c>
       <c r="D193" t="inlineStr">
@@ -13717,7 +13717,7 @@
       </c>
       <c r="C194" s="3" t="inlineStr">
         <is>
-          <t>【悪の力、火の力、水の力】攻撃時に敵の特攻、特防、物攻、物防を減少し、自身の属性に敵の減少した属性を追加する。同時に【悪の力、火の力、水の力】を獲得し、味方全体が追加で吸血効果を10%獲得する。</t>
+          <t>【邪恶之力、火之力、水之力】攻击时减少敌人的特攻、特防、物攻、物防，在自身属性上追加敌人减少的属性。同时获得【邪恶之力、火之力、水之力】，全体伙伴额外获得10%吸血效果。</t>
         </is>
       </c>
       <c r="D194" t="inlineStr">
@@ -13774,7 +13774,7 @@
       </c>
       <c r="C195" s="3" t="inlineStr">
         <is>
-          <t>【日の石】行動ターン開始前に怒気を200回復し、同時に【日月の石】を所持する場合、覚醒値の回復速度が30%上昇する。</t>
+          <t>【日之石】行动回合开始前回复200怒气，同时持有【日月石】时，觉醒值回复速度上升30%。</t>
         </is>
       </c>
       <c r="D195" t="inlineStr">
@@ -13831,7 +13831,7 @@
       </c>
       <c r="C196" s="3" t="inlineStr">
         <is>
-          <t>【月の石】ターン終了後、自身が失ったHP10%を回復し、同時に【日月の石】を所持する場合、覚醒値の回復速度が30%上昇する。</t>
+          <t>【月之石】回合结束后，回复自身失去的HP10%，同时持有【月之石】时，觉醒值回复速度上升30%。</t>
         </is>
       </c>
       <c r="D196" t="inlineStr">
@@ -13888,7 +13888,7 @@
       </c>
       <c r="C197" s="3" t="inlineStr">
         <is>
-          <t>【怒火】戦闘開始時、味方全体が覚醒値を100獲得し、その他【憤怒、憤激、怒りの吸収、激怒、暴怒】の各効果は覚醒値を100上昇する。</t>
+          <t>【怒火】战斗开始时，我方全体获得100觉醒值，其他【愤怒、激愤、吸收愤怒、激怒、暴怒】各效果觉醒值上升100。</t>
         </is>
       </c>
       <c r="D197" t="inlineStr">
@@ -13945,7 +13945,7 @@
       </c>
       <c r="C198" s="3" t="inlineStr">
         <is>
-          <t>【憤怒】ダメージを受けた時、覚醒値を100獲得し、【怒火】の覚醒値を上昇する。</t>
+          <t>受到【愤怒】伤害时，获得100点觉醒值，提升【怒火】的觉醒值。</t>
         </is>
       </c>
       <c r="D198" t="inlineStr">
@@ -14007,7 +14007,7 @@
       </c>
       <c r="C199" s="3" t="inlineStr">
         <is>
-          <t>【憤激】味方が敵を撃破した時、自身のHP10%と覚醒値200を回復し、【怒火】の覚醒値を上昇する。</t>
+          <t>【激愤】我方击破敌人时，回复自身HP10%和觉醒值200，使【怒火】觉醒值上升。</t>
         </is>
       </c>
       <c r="D199" t="inlineStr">
@@ -14069,7 +14069,7 @@
       </c>
       <c r="C200" s="3" t="inlineStr">
         <is>
-          <t>【怒りの吸収】味方の攻撃時、30%の確率で敵の覚醒値を100奪取し、【怒火】の覚醒値を上昇する。</t>
+          <t>【愤怒吸收】我方攻击时，有30%几率夺取敌人100觉醒值，使【怒火】觉醒值上升。</t>
         </is>
       </c>
       <c r="D200" t="inlineStr">
@@ -14131,7 +14131,7 @@
       </c>
       <c r="C201" s="3" t="inlineStr">
         <is>
-          <t>【激怒】：小スキルまたは通常攻撃使用時、ゲージ値を100追加獲得できる（【怒火】のゲージ値が増加）</t>
+          <t>【激怒】：使用小技能或普通攻击时，可额外获得100计量值（【怒火】的计量值增加）</t>
         </is>
       </c>
       <c r="D201" t="inlineStr">
@@ -14193,7 +14193,7 @@
       </c>
       <c r="C202" s="3" t="inlineStr">
         <is>
-          <t>【暴怒】必殺スキル以外を発動した時、覚醒値1%ごとにダメージバフを1%付与してダメージを与え、【怒火】の覚醒値が上昇する。</t>
+          <t>【暴怒】必杀技能以外发动时，觉醒值每1%给予伤害增益 1%的伤害，【怒火】觉醒值上升。</t>
         </is>
       </c>
       <c r="D202" t="inlineStr">
@@ -14255,7 +14255,7 @@
       </c>
       <c r="C203" s="3" t="inlineStr">
         <is>
-          <t>【シールド生成】戦闘開始時、味方全体に自身のHP10%のダメージを吸収するシールドを生成する。その他【シールド防御、シールド耐性、盾愈、シールド攻撃、シールド弱化、シールド強化】の効果を1つあるごとにシールド生成量が4%増加する。</t>
+          <t>【护盾生成】战斗开始时，生成能吸收自身生命值10%伤害的护盾。其他【护盾防御、护盾抗性、护盾治愈、护盾攻击、护盾弱化、护盾强化】效果每增加一个，护盾生成量增加4%。</t>
         </is>
       </c>
       <c r="D203" t="inlineStr">
@@ -14312,7 +14312,7 @@
       </c>
       <c r="C204" s="3" t="inlineStr">
         <is>
-          <t>【シールド防御】シールド持続中、20%の物防と物防を付与し、【シールド生成】のシールド量が増加する。</t>
+          <t>【护盾防御】护盾持续中，给予20%的物防和物防，【护盾生成】的护盾量增加。</t>
         </is>
       </c>
       <c r="D204" t="inlineStr">
@@ -14374,7 +14374,7 @@
       </c>
       <c r="C205" s="3" t="inlineStr">
         <is>
-          <t>【シールド耐性】シールド持続中、制御とデバフ効果を無効化し、【シールド生成】のシールド量が増加する。</t>
+          <t>【护盾耐性】护盾持续中，控制和减益效果无效化，【护盾生成】的护盾量增加。</t>
         </is>
       </c>
       <c r="D205" t="inlineStr">
@@ -14436,7 +14436,7 @@
       </c>
       <c r="C206" s="3" t="inlineStr">
         <is>
-          <t>【シールド攻撃】攻撃のたびに自身の現在のシールド値20%の確定ダメージを付与し、【シールド生成】のシールド量が増加する。</t>
+          <t>【护盾攻击】每次攻击给予自身当前护盾值20%的真实伤害，增加【护盾生成】的护盾量。</t>
         </is>
       </c>
       <c r="D206" t="inlineStr">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="C207" s="3" t="inlineStr">
         <is>
-          <t>【シールド強化】会心攻撃を受けた時、味方全体が自身の最大HP10%のシールドを獲得し、【シールド生成】のシールド量が増加する。</t>
+          <t>【护盾强化】受到会心攻击时，我方全体获得自身最大HP10%的护盾，【护盾生成】的护盾量增加。</t>
         </is>
       </c>
       <c r="D207" t="inlineStr">
@@ -14560,7 +14560,7 @@
       </c>
       <c r="C208" s="3" t="inlineStr">
         <is>
-          <t>【シールド弱体化】シールド爆破時、敵全体にHP上限6%のHPを付与し、【シールド生成】のシールド量が増加する。</t>
+          <t>【护盾弱化】护盾爆破时，给予全体敌人6%的生命值上限，增加【护盾生成】的护盾量。</t>
         </is>
       </c>
       <c r="D208" t="inlineStr">
@@ -14622,7 +14622,7 @@
       </c>
       <c r="C209" s="3" t="inlineStr">
         <is>
-          <t>【シールド治癒】シールド爆破時、自身のHP上限5%のHPを回復し、【シールド生成】のシールド量が増加する。</t>
+          <t>【护盾治愈】护盾爆破时，回复自身5%的生命值上限，增加【护盾生成】的护盾量。</t>
         </is>
       </c>
       <c r="D209" t="inlineStr">
@@ -14692,7 +14692,7 @@
       </c>
       <c r="C212" s="3" t="inlineStr">
         <is>
-          <t>【破竹の勢い】HPが70%以上の敵1体に30%の追加ダメージを与える。【破竹の勢い】と【秋風に舞う落ち葉】の効果を同時に持つ場合、会心率が追加で20%上昇する。</t>
+          <t>【破竹之势】对一个生命值在70%以上的敌人造成30%的额外伤害。同时拥有【破竹之势】和【秋风飘舞的落叶】效果时，暴击率额外上升20%。</t>
         </is>
       </c>
       <c r="D212" t="inlineStr">
@@ -14754,7 +14754,7 @@
       </c>
       <c r="C213" s="3" t="inlineStr">
         <is>
-          <t>【秋風に舞う落ち葉】HPが30%以下の敵1体に40%のダメージを追加で与える。【破竹の勢い】と【秋風に舞う落ち葉】の効果を同時に持つ場合、会心率が追加で20%上昇する。</t>
+          <t>【秋风飘舞的落叶】对一个生命值在30%以下的敌人追加40%的伤害。同时拥有【破竹之势】和【秋风飘舞的落叶】效果时，暴击率额外上升20%。</t>
         </is>
       </c>
       <c r="D213" t="inlineStr">
@@ -14816,7 +14816,7 @@
       </c>
       <c r="C214" s="3" t="inlineStr">
         <is>
-          <t>【血襲】味方が1%吸血ごとにダメージバフが5%上昇する。【血襲】と【バットウィング】の効果を同時に持つ場合、味方が1%吸血ごとに敵の物防と物防を1%奪取する。</t>
+          <t>【血袭】我方每吸1%血，伤害增益提升5%。同时拥有【血袭】和【蝙蝠翼】效果时，我方每吸1%血夺取敌人1%物防和1%物防。</t>
         </is>
       </c>
       <c r="D214" t="inlineStr">
@@ -14878,7 +14878,7 @@
       </c>
       <c r="C215" s="3" t="inlineStr">
         <is>
-          <t>【バットウィング】味方が1%吸血ごとに速度が5%上昇する。【血襲】と【バットウィング】の効果を同時に持つ場合、味方が1%吸血ごとに敵の物防と物防を1%奪取する。</t>
+          <t>【蝙蝠翼】我方每吸1%血，速度上升5%。同时拥有【血袭】和【蝙蝠翼】效果时，我方每吸1%血夺取敌人1%物防和1%物防。</t>
         </is>
       </c>
       <c r="D215" t="inlineStr">
@@ -14940,7 +14940,7 @@
       </c>
       <c r="C216" s="3" t="inlineStr">
         <is>
-          <t>【毒蝕】攻撃時に50%の確率で中毒効果を付与し、【毒蝕】、【染血】、【引火】の効果を同時に持つ場合、味方の与える持続ダメージが100%上昇する(5段重複可能)。</t>
+          <t>【毒蚀】攻击时有50%的机率附加中毒效果，同时拥有【毒蚀】、【染血】、【引火】效果时，我方给予的持续伤害上升100%（5段可重复）。</t>
         </is>
       </c>
       <c r="D216" t="inlineStr">
@@ -15002,7 +15002,7 @@
       </c>
       <c r="C217" s="3" t="inlineStr">
         <is>
-          <t>【染血】攻撃時に50%の確率で流血効果を付与し、【毒蝕】、【染血】、【引火】の効果を同時に持つ場合、味方の与える持続ダメージが100%上昇する(5段重複可能)。</t>
+          <t>【染血】攻击时有50%几率施加流血效果，同时拥有【毒蚀】、【染血】、【闪点】效果时，我方给予的持续伤害上升100%（5段可重复）。</t>
         </is>
       </c>
       <c r="D217" t="inlineStr">
@@ -15064,7 +15064,7 @@
       </c>
       <c r="C218" s="3" t="inlineStr">
         <is>
-          <t>【引火】攻撃時に50%の確率で火傷効果を付与し、【毒蝕】、【染血】、【引火】の効果を同時に持つ場合、味方の与える持続ダメージが100%上昇する(5段重複可能)。</t>
+          <t>【闪点】攻击时有50%几率施加烧伤效果，同时拥有【毒蚀】、【染血】、【闪点】效果时，我方给予的持续伤害上升100%（5段可重复）。</t>
         </is>
       </c>
       <c r="D218" t="inlineStr">
@@ -15127,7 +15127,7 @@
       </c>
       <c r="C220" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+10%</t>
+          <t>我方的物攻和特攻+10%</t>
         </is>
       </c>
       <c r="D220" t="inlineStr">
@@ -15204,7 +15204,7 @@
       </c>
       <c r="C221" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+10%</t>
+          <t>我方的物攻和特攻+10%</t>
         </is>
       </c>
       <c r="D221" t="inlineStr">
@@ -15281,7 +15281,7 @@
       </c>
       <c r="C222" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D222" t="inlineStr">
@@ -15358,7 +15358,7 @@
       </c>
       <c r="C223" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+5%</t>
+          <t>我方的物攻和特攻+5%</t>
         </is>
       </c>
       <c r="D223" t="inlineStr">
@@ -15435,7 +15435,7 @@
       </c>
       <c r="C224" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+10%</t>
+          <t>我方的物攻和特攻+10%</t>
         </is>
       </c>
       <c r="D224" t="inlineStr">
@@ -15512,7 +15512,7 @@
       </c>
       <c r="C225" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+10%</t>
+          <t>我方的物攻和特攻+10%</t>
         </is>
       </c>
       <c r="D225" t="inlineStr">
@@ -15589,7 +15589,7 @@
       </c>
       <c r="C226" t="inlineStr">
         <is>
-          <t>味方の物攻と特攻+10%</t>
+          <t>我方的物攻和特攻+10%</t>
         </is>
       </c>
       <c r="D226" t="inlineStr">
